--- a/business_forms/045_employee_benefit_enrollment_form--business_forms.xlsx
+++ b/business_forms/045_employee_benefit_enrollment_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'medical',_'value':_'medical'}</t>
+          <t>medical</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Medical', 'value': 'medical'}</t>
+          <t>Medical</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'dental',_'value':_'dental'}</t>
+          <t>dental</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Dental', 'value': 'dental'}</t>
+          <t>Dental</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'vision',_'value':_'vision'}</t>
+          <t>vision</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Vision', 'value': 'vision'}</t>
+          <t>Vision</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'aetna',_'value':_'aetna'}</t>
+          <t>aetna</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Aetna', 'value': 'Aetna'}</t>
+          <t>Aetna</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'blue_cross',_'value':_'blue_cross'}</t>
+          <t>blue_cross</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Blue Cross', 'value': 'Blue Cross'}</t>
+          <t>Blue Cross</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'cigna',_'value':_'cigna'}</t>
+          <t>cigna</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Cigna', 'value': 'Cigna'}</t>
+          <t>Cigna</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'active',_'value':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Active', 'value': 'active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'inactive',_'value':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Inactive', 'value': 'inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'sales',_'value':_'sales'}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Sales', 'value': 'sales'}</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'marketing',_'value':_'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Marketing', 'value': 'marketing'}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'customer_support',_'value':_'customer_support'}</t>
+          <t>customer_support</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Customer Support', 'value': 'customer_support'}</t>
+          <t>Customer Support</t>
         </is>
       </c>
     </row>
